--- a/data_figures.xlsx
+++ b/data_figures.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,33 +441,32 @@
           <t>Year</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr"/>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Count (Non-COVID-19-related)</t>
+        </is>
+      </c>
       <c r="C1" s="2" t="inlineStr">
         <is>
-          <t>Count (Non-COVID-19-related)</t>
+          <t>Count (COVID-19-related)</t>
         </is>
       </c>
       <c r="D1" s="2" t="inlineStr">
         <is>
-          <t>Count (COVID-19-related)</t>
+          <t>Paper-published-total</t>
         </is>
       </c>
       <c r="E1" s="2" t="inlineStr">
         <is>
-          <t>Paper-published-total</t>
+          <t>Count (Total)</t>
         </is>
       </c>
       <c r="F1" s="2" t="inlineStr">
         <is>
-          <t>Count (Total)</t>
+          <t>Normalized (Non-COVID-19-related)</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
-        <is>
-          <t>Normalized (Non-COVID-19-related)</t>
-        </is>
-      </c>
-      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>Normalized (COVID-19-related)</t>
         </is>
@@ -480,24 +479,21 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
+        <v>140</v>
       </c>
       <c r="C2" t="n">
-        <v>139</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>1351945</v>
       </c>
       <c r="E2" t="n">
-        <v>1351945</v>
+        <v>140</v>
       </c>
       <c r="F2" t="n">
-        <v>139</v>
+        <v>10.3554508504414</v>
       </c>
       <c r="G2" t="n">
-        <v>10.28148334436682</v>
-      </c>
-      <c r="H2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -508,24 +504,21 @@
         </is>
       </c>
       <c r="B3" t="n">
+        <v>148</v>
+      </c>
+      <c r="C3" t="n">
         <v>0</v>
       </c>
-      <c r="C3" t="n">
+      <c r="D3" t="n">
+        <v>1417896</v>
+      </c>
+      <c r="E3" t="n">
         <v>148</v>
       </c>
-      <c r="D3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" t="n">
-        <v>1417896</v>
-      </c>
       <c r="F3" t="n">
-        <v>148</v>
+        <v>10.43800109457957</v>
       </c>
       <c r="G3" t="n">
-        <v>10.43800109457957</v>
-      </c>
-      <c r="H3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -536,24 +529,21 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>179</v>
       </c>
       <c r="C4" t="n">
-        <v>179</v>
+        <v>8</v>
       </c>
       <c r="D4" t="n">
-        <v>8</v>
+        <v>1640716</v>
       </c>
       <c r="E4" t="n">
-        <v>1640716</v>
+        <v>187</v>
       </c>
       <c r="F4" t="n">
-        <v>187</v>
+        <v>10.90987105629493</v>
       </c>
       <c r="G4" t="n">
-        <v>10.90987105629493</v>
-      </c>
-      <c r="H4" t="n">
         <v>0.4875920025159747</v>
       </c>
     </row>
@@ -564,24 +554,21 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>224</v>
       </c>
       <c r="C5" t="n">
-        <v>224</v>
+        <v>55</v>
       </c>
       <c r="D5" t="n">
-        <v>55</v>
+        <v>1786726</v>
       </c>
       <c r="E5" t="n">
-        <v>1786726</v>
+        <v>279</v>
       </c>
       <c r="F5" t="n">
-        <v>279</v>
+        <v>12.53689709558153</v>
       </c>
       <c r="G5" t="n">
-        <v>12.53689709558153</v>
-      </c>
-      <c r="H5" t="n">
         <v>3.078255983290107</v>
       </c>
     </row>
@@ -592,24 +579,21 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>267</v>
       </c>
       <c r="C6" t="n">
-        <v>267</v>
+        <v>63</v>
       </c>
       <c r="D6" t="n">
-        <v>63</v>
+        <v>1778030</v>
       </c>
       <c r="E6" t="n">
-        <v>1778030</v>
+        <v>330</v>
       </c>
       <c r="F6" t="n">
-        <v>330</v>
+        <v>15.01661951710601</v>
       </c>
       <c r="G6" t="n">
-        <v>15.01661951710601</v>
-      </c>
-      <c r="H6" t="n">
         <v>3.543247301789059</v>
       </c>
     </row>
@@ -624,7 +608,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -671,10 +655,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="C2" t="n">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -687,10 +671,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>53.19767441860465</v>
+        <v>53.06122448979592</v>
       </c>
       <c r="G2" t="n">
-        <v>54.65116279069768</v>
+        <v>54.71331389698737</v>
       </c>
     </row>
     <row r="3">
@@ -703,7 +687,7 @@
         <v>187</v>
       </c>
       <c r="C3" t="n">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -716,10 +700,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>18.12015503875969</v>
+        <v>18.17298347910593</v>
       </c>
       <c r="G3" t="n">
-        <v>17.82945736434108</v>
+        <v>17.97862001943635</v>
       </c>
     </row>
     <row r="4">
@@ -729,10 +713,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C4" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -745,10 +729,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>5.135658914728682</v>
+        <v>5.247813411078718</v>
       </c>
       <c r="G4" t="n">
-        <v>5.038759689922481</v>
+        <v>5.247813411078718</v>
       </c>
     </row>
     <row r="5">
@@ -774,10 +758,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3.875968992248062</v>
+        <v>3.887269193391643</v>
       </c>
       <c r="G5" t="n">
-        <v>3.488372093023256</v>
+        <v>3.498542274052478</v>
       </c>
     </row>
     <row r="6">
@@ -803,68 +787,39 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.228682170542636</v>
+        <v>2.235179786200194</v>
       </c>
       <c r="G6" t="n">
-        <v>1.550387596899225</v>
+        <v>1.554907677356657</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>other</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>21</v>
+        <v>179</v>
       </c>
       <c r="C7" t="n">
-        <v>18</v>
+        <v>175</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>other</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Asia</t>
+          <t>other</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.034883720930233</v>
+        <v>17.3955296404276</v>
       </c>
       <c r="G7" t="n">
-        <v>1.744186046511628</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>159</v>
-      </c>
-      <c r="C8" t="n">
-        <v>162</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>15.40697674418605</v>
-      </c>
-      <c r="G8" t="n">
-        <v>15.69767441860465</v>
+        <v>17.00680272108843</v>
       </c>
     </row>
   </sheetData>
@@ -1336,7 +1291,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -1352,7 +1307,7 @@
         <v>824284</v>
       </c>
       <c r="F18" t="n">
-        <v>0.01334491510207647</v>
+        <v>0.0121317410018877</v>
       </c>
     </row>
     <row r="19">
@@ -1462,7 +1417,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -1478,7 +1433,7 @@
         <v>330877</v>
       </c>
       <c r="F24" t="n">
-        <v>0.5349419875059312</v>
+        <v>0.5379642586217839</v>
       </c>
     </row>
     <row r="25">
@@ -1488,7 +1443,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -1504,7 +1459,7 @@
         <v>1156262</v>
       </c>
       <c r="F25" t="n">
-        <v>0.4609681888706885</v>
+        <v>0.4618330447597517</v>
       </c>
     </row>
     <row r="26">
@@ -1514,7 +1469,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -1530,7 +1485,7 @@
         <v>178579</v>
       </c>
       <c r="F26" t="n">
-        <v>0.2855878910734185</v>
+        <v>0.2967874162135525</v>
       </c>
     </row>
     <row r="27">
@@ -4291,10 +4246,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C2" t="n">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -4303,13 +4258,13 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="F2" t="n">
-        <v>18.51851851851852</v>
+        <v>18.44660194174757</v>
       </c>
       <c r="G2" t="n">
-        <v>54.46247464503043</v>
+        <v>54.39838220424672</v>
       </c>
     </row>
     <row r="3">
@@ -4322,7 +4277,7 @@
         <v>15</v>
       </c>
       <c r="C3" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -4331,13 +4286,13 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F3" t="n">
-        <v>6.944444444444445</v>
+        <v>7.281553398058253</v>
       </c>
       <c r="G3" t="n">
-        <v>18.45841784989858</v>
+        <v>18.50353892821031</v>
       </c>
     </row>
     <row r="4">
@@ -4361,64 +4316,64 @@
         <v>47</v>
       </c>
       <c r="F4" t="n">
-        <v>5.555555555555555</v>
+        <v>5.825242718446602</v>
       </c>
       <c r="G4" t="n">
-        <v>3.549695740365112</v>
+        <v>3.538928210313448</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>10</v>
       </c>
       <c r="C5" t="n">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>61</v>
+        <v>22</v>
       </c>
       <c r="F5" t="n">
-        <v>4.62962962962963</v>
+        <v>4.854368932038835</v>
       </c>
       <c r="G5" t="n">
-        <v>5.172413793103448</v>
+        <v>1.213346814964611</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C6" t="n">
-        <v>12</v>
+        <v>53</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>22</v>
+        <v>62</v>
       </c>
       <c r="F6" t="n">
-        <v>4.62962962962963</v>
+        <v>4.368932038834951</v>
       </c>
       <c r="G6" t="n">
-        <v>1.217038539553753</v>
+        <v>5.358948432760364</v>
       </c>
     </row>
     <row r="7">
@@ -4442,10 +4397,10 @@
         <v>20</v>
       </c>
       <c r="F7" t="n">
-        <v>4.166666666666667</v>
+        <v>4.368932038834951</v>
       </c>
       <c r="G7" t="n">
-        <v>1.115618661257606</v>
+        <v>1.112234580384226</v>
       </c>
     </row>
     <row r="8">
@@ -4455,7 +4410,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C8" t="n">
         <v>18</v>
@@ -4466,13 +4421,13 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F8" t="n">
-        <v>1.388888888888889</v>
+        <v>1.941747572815534</v>
       </c>
       <c r="G8" t="n">
-        <v>1.825557809330629</v>
+        <v>1.820020222446916</v>
       </c>
     </row>
     <row r="9">
@@ -4496,10 +4451,10 @@
         <v>23</v>
       </c>
       <c r="F9" t="n">
-        <v>1.388888888888889</v>
+        <v>1.456310679611651</v>
       </c>
       <c r="G9" t="n">
-        <v>2.028397565922921</v>
+        <v>2.022244691607685</v>
       </c>
     </row>
     <row r="10">
@@ -4509,10 +4464,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="C10" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -4520,10 +4475,10 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>52.77777777777778</v>
+        <v>51.45631067961164</v>
       </c>
       <c r="G10" t="n">
-        <v>12.17038539553752</v>
+        <v>12.03235591506572</v>
       </c>
     </row>
   </sheetData>
@@ -4537,7 +4492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D44"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4609,7 +4564,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -4619,7 +4574,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -4631,7 +4586,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -4641,7 +4596,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -4653,7 +4608,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -4663,7 +4618,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -4697,29 +4652,29 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>United States</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4729,7 +4684,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -4741,44 +4696,44 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
           <t>US</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>GB</t>
-        </is>
-      </c>
       <c r="C10" t="inlineStr">
         <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
           <t>United States</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>US</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>United Kingdom</t>
         </is>
       </c>
     </row>
@@ -4807,22 +4762,22 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Spain</t>
         </is>
       </c>
     </row>
@@ -4851,7 +4806,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -4861,7 +4816,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -4895,7 +4850,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -4905,7 +4860,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -4917,44 +4872,44 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>United States</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>United States</t>
         </is>
       </c>
     </row>
@@ -4983,73 +4938,73 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>United States</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>United States</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>United States</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5059,7 +5014,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5071,22 +5026,22 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>United Kingdom</t>
         </is>
       </c>
     </row>
@@ -5115,51 +5070,51 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Spain</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>US</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>United Kingdom</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5169,7 +5124,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -5181,29 +5136,29 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Spain</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -5213,7 +5168,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5225,22 +5180,22 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
           <t>US</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>GB</t>
-        </is>
-      </c>
       <c r="C32" t="inlineStr">
         <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
           <t>United States</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
         </is>
       </c>
     </row>
@@ -5252,7 +5207,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -5262,249 +5217,29 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>United States</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>United States</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>GB</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
           <t>Spain</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>GB</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>GB</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>AU</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Australia</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>GB</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Spain</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>JP</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Japan</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>CH</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Switzerland</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Canada</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Germany</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>GB</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>GB</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>United States</t>
         </is>
       </c>
     </row>
@@ -5519,7 +5254,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5551,7 +5286,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -5571,7 +5306,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -5591,7 +5326,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -5631,7 +5366,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -5671,7 +5406,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -5687,15 +5422,15 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>TriNetX</t>
+          <t>IBM</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>TriNetX</t>
+          <t>IBM</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -5707,15 +5442,15 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>TriNetX</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>TriNetX</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -5733,6 +5468,16 @@
       <c r="B11" t="n">
         <v>11</v>
       </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>InGef</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -5741,7 +5486,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -5755,58 +5500,23 @@
       </c>
     </row>
     <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>IQVIA</t>
+        </is>
+      </c>
       <c r="B13" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>The Health Improvement Network</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>New York University Langone Health</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Western Australian Data Linkage System</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>5</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>WADLS</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Australia</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>University of Minnesota</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>5</v>
+        <v>10</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>IQVIA</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -5820,7 +5530,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B424"/>
+  <dimension ref="A1:B451"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5838,31 +5548,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Flatiron</t>
+          <t>SAIL</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>II) Neoplasms</t>
+          <t>other</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Flatiron</t>
+          <t>CPRD</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>II) Neoplasms</t>
+          <t>other</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Flatiron</t>
+          <t>Cerner</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -5874,19 +5584,19 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Flatiron</t>
+          <t>Cerner</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>II) Neoplasms</t>
+          <t>IX) Diseases of the circulatory system</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Cerner</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -5898,36 +5608,36 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SAIL</t>
+          <t>Cerner</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>X) Diseases of the respiratory system</t>
+          <t>other</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CPRD</t>
+          <t>Cerner</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>X) Diseases of the respiratory system</t>
+          <t>V) Mental and behavioural disorders</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Cerner</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>II) Neoplasms</t>
+          <t>XXII) Codes for special purposes (COVID-19)</t>
         </is>
       </c>
     </row>
@@ -5939,127 +5649,127 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>II) Neoplasms</t>
+          <t>other</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>VUMC</t>
+          <t>Cerner</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>V) Mental and behavioural disorders</t>
+          <t>other</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>Cerner</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>XXII) Codes for special purposes (COVID-19)</t>
+          <t>IV) Endocrine, nutritional and metabolic diseases</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Cerner</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>IV) Endocrine, nutritional and metabolic diseases</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>VUMC</t>
+          <t>Cerner</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>XIII) Diseases of the musculoskeletal system and connective tissue</t>
+          <t>IX) Diseases of the circulatory system</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Cerner</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>XXII) Codes for special purposes (COVID-19)</t>
+          <t>other</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>VUMC</t>
+          <t>Cerner</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>XIII) Diseases of the musculoskeletal system and connective tissue</t>
+          <t>other</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Flatiron</t>
+          <t>IQVIA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>II) Neoplasms</t>
+          <t>IX) Diseases of the circulatory system</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Flatiron</t>
+          <t>Cerner</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>II) Neoplasms</t>
+          <t>other</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Flatiron</t>
+          <t>Cerner</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>II) Neoplasms</t>
+          <t>other</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>IQVIA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>I) Certain infectious and parasitic diseases</t>
+          <t>other</t>
         </is>
       </c>
     </row>
@@ -6071,55 +5781,55 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>IX) Diseases of the circulatory system</t>
+          <t>other</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>Cerner</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>IX) Diseases of the circulatory system</t>
+          <t>other</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Flatiron</t>
+          <t>Cerner</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>II) Neoplasms</t>
+          <t>V) Mental and behavioural disorders</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Cerner</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>VI) Diseases of the nervous system</t>
+          <t>other</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>Cerner</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>IX) Diseases of the circulatory system</t>
+          <t>IV) Endocrine, nutritional and metabolic diseases</t>
         </is>
       </c>
     </row>
@@ -6138,19 +5848,19 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Cerner</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>XXII) Codes for special purposes (COVID-19)</t>
+          <t>IX) Diseases of the circulatory system</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Cerner</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -6167,26 +5877,26 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>VI) Diseases of the nervous system</t>
+          <t>XXII) Codes for special purposes (COVID-19)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>VUMC</t>
+          <t>SAIL</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>X) Diseases of the respiratory system</t>
+          <t>V) Mental and behavioural disorders</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SAIL</t>
+          <t>SLaM NHS</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -6198,60 +5908,60 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Cerner</t>
+          <t>Flatiron</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>II) Neoplasms</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Flatiron</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>II) Neoplasms</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Flatiron</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>VI) Diseases of the nervous system</t>
+          <t>II) Neoplasms</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>SLaM NHS</t>
+          <t>Flatiron</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>V) Mental and behavioural disorders</t>
+          <t>II) Neoplasms</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Flatiron</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>II) Neoplasms</t>
         </is>
       </c>
     </row>
@@ -6270,64 +5980,69 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>IQVIA</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>XIII) Diseases of the musculoskeletal system and connective tissue</t>
+          <t>other</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Flatiron</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>II) Neoplasms</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Flatiron</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>V) Mental and behavioural disorders</t>
+          <t>II) Neoplasms</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Flatiron</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>I) Certain infectious and parasitic diseases</t>
+          <t>II) Neoplasms</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Flatiron</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>VI) Diseases of the nervous system</t>
+          <t>II) Neoplasms</t>
         </is>
       </c>
     </row>
     <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Flatiron</t>
+        </is>
+      </c>
       <c r="B43" t="inlineStr">
         <is>
           <t>II) Neoplasms</t>
@@ -6337,12 +6052,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>VUMC</t>
+          <t>IQVIA</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>XIII) Diseases of the musculoskeletal system and connective tissue</t>
+          <t>other</t>
         </is>
       </c>
     </row>
@@ -6373,24 +6088,24 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Flatiron</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>II) Neoplasms</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Flatiron</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>V) Mental and behavioural disorders</t>
+          <t>II) Neoplasms</t>
         </is>
       </c>
     </row>
@@ -6409,168 +6124,168 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>VUMC</t>
+          <t>Flatiron</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>XIII) Diseases of the musculoskeletal system and connective tissue</t>
+          <t>II) Neoplasms</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Flatiron</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>V) Mental and behavioural disorders</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>Flatiron</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>II) Neoplasms</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Flatiron</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>IX) Diseases of the circulatory system</t>
+          <t>II) Neoplasms</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>Flatiron</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>V) Mental and behavioural disorders</t>
+          <t>II) Neoplasms</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Flatiron</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>IX) Diseases of the circulatory system</t>
+          <t>II) Neoplasms</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Flatiron</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>XXII) Codes for special purposes (COVID-19)</t>
+          <t>II) Neoplasms</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Flatiron</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>IX) Diseases of the circulatory system</t>
+          <t>II) Neoplasms</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Flatiron</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>VI) Diseases of the nervous system</t>
+          <t>II) Neoplasms</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>VUMC</t>
+          <t>IQVIA</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>II) Neoplasms</t>
+          <t>other</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>VUMC</t>
+          <t>Flatiron</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>V) Mental and behavioural disorders</t>
+          <t>II) Neoplasms</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Cerner</t>
+          <t>Flatiron</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>V) Mental and behavioural disorders</t>
+          <t>II) Neoplasms</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>CPRD</t>
+          <t>Flatiron</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>X) Diseases of the respiratory system</t>
+          <t>II) Neoplasms</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Flatiron</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>IX) Diseases of the circulatory system</t>
+          <t>II) Neoplasms</t>
         </is>
       </c>
     </row>
@@ -6625,36 +6340,36 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Cerner</t>
+          <t>Flatiron</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>XXII) Codes for special purposes (COVID-19)</t>
+          <t>II) Neoplasms</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Flatiron</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>VI) Diseases of the nervous system</t>
+          <t>II) Neoplasms</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Flatiron</t>
+          <t>CPRD</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>II) Neoplasms</t>
+          <t>other</t>
         </is>
       </c>
     </row>
@@ -6685,19 +6400,19 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>VUMC</t>
+          <t>Flatiron</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>V) Mental and behavioural disorders</t>
+          <t>II) Neoplasms</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>NPS</t>
+          <t>IQVIA</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6709,12 +6424,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Flatiron</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>II) Neoplasms</t>
         </is>
       </c>
     </row>
@@ -6726,19 +6441,19 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>V) Mental and behavioural disorders</t>
+          <t>II) Neoplasms</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>SLaM NHS</t>
+          <t>Flatiron</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>V) Mental and behavioural disorders</t>
+          <t>II) Neoplasms</t>
         </is>
       </c>
     </row>
@@ -6757,12 +6472,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>VUMC</t>
+          <t>Flatiron</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>IX) Diseases of the circulatory system</t>
+          <t>II) Neoplasms</t>
         </is>
       </c>
     </row>
@@ -6781,96 +6496,96 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>SAIL</t>
+          <t>Flatiron</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>XXII) Codes for special purposes (COVID-19)</t>
+          <t>II) Neoplasms</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Flatiron</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>IX) Diseases of the circulatory system</t>
+          <t>II) Neoplasms</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Cerner</t>
+          <t>Flatiron</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>II) Neoplasms</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>VUMC</t>
+          <t>Flatiron</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>IV) Endocrine, nutritional and metabolic diseases</t>
+          <t>II) Neoplasms</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>Flatiron</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>II) Neoplasms</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>TriNetX</t>
+          <t>Flatiron</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>II) Neoplasms</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>TriNetX</t>
+          <t>Flatiron</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>XXII) Codes for special purposes (COVID-19)</t>
+          <t>II) Neoplasms</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Flatiron</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>IV) Endocrine, nutritional and metabolic diseases</t>
+          <t>II) Neoplasms</t>
         </is>
       </c>
     </row>
@@ -6889,24 +6604,24 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>NPS</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>II) Neoplasms</t>
+          <t>other</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Flatiron</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>IV) Endocrine, nutritional and metabolic diseases</t>
+          <t>II) Neoplasms</t>
         </is>
       </c>
     </row>
@@ -6925,67 +6640,67 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>SAIL</t>
+          <t>Flatiron</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>IV) Endocrine, nutritional and metabolic diseases</t>
+          <t>II) Neoplasms</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>SLaM NHS</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>I) Certain infectious and parasitic diseases</t>
+          <t>V) Mental and behavioural disorders</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>SAIL</t>
+          <t>Flatiron</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>IV) Endocrine, nutritional and metabolic diseases</t>
+          <t>II) Neoplasms</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>VUMC</t>
+          <t>Flatiron</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>XIII) Diseases of the musculoskeletal system and connective tissue</t>
+          <t>II) Neoplasms</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Flatiron</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>IV) Endocrine, nutritional and metabolic diseases</t>
+          <t>II) Neoplasms</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>VUMC</t>
+          <t>IQVIA</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6997,19 +6712,19 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>VUMC</t>
+          <t>SAIL</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>XIII) Diseases of the musculoskeletal system and connective tissue</t>
+          <t>XXII) Codes for special purposes (COVID-19)</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Flatiron</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -7021,19 +6736,19 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Flatiron</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>IX) Diseases of the circulatory system</t>
+          <t>II) Neoplasms</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Flatiron</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -7057,120 +6772,115 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>Flatiron</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>II) Neoplasms</t>
         </is>
       </c>
     </row>
     <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>SAIL</t>
-        </is>
-      </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>V) Mental and behavioural disorders</t>
+          <t>other</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>VUMC</t>
+          <t>Flatiron</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>IX) Diseases of the circulatory system</t>
+          <t>II) Neoplasms</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Flatiron</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>IX) Diseases of the circulatory system</t>
+          <t>II) Neoplasms</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>Flatiron</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>II) Neoplasms</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>CPRD</t>
+          <t>Flatiron</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>I) Certain infectious and parasitic diseases</t>
+          <t>II) Neoplasms</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>CPRD</t>
+          <t>Flatiron</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>IV) Endocrine, nutritional and metabolic diseases</t>
+          <t>II) Neoplasms</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>Flatiron</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>VI) Diseases of the nervous system</t>
+          <t>II) Neoplasms</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Flatiron</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>IX) Diseases of the circulatory system</t>
+          <t>II) Neoplasms</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Flatiron</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>XXII) Codes for special purposes (COVID-19)</t>
+          <t>II) Neoplasms</t>
         </is>
       </c>
     </row>
@@ -7189,12 +6899,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>CPRD</t>
+          <t>Flatiron</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>X) Diseases of the respiratory system</t>
+          <t>II) Neoplasms</t>
         </is>
       </c>
     </row>
@@ -7213,19 +6923,19 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Flatiron</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>II) Neoplasms</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>TriNetX</t>
+          <t>Flatiron</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -7247,45 +6957,50 @@
       </c>
     </row>
     <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Flatiron</t>
+        </is>
+      </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>IX) Diseases of the circulatory system</t>
+          <t>II) Neoplasms</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>WADLS</t>
+          <t>Flatiron</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>II) Neoplasms</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>Flatiron</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>II) Neoplasms</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Flatiron</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>IX) Diseases of the circulatory system</t>
+          <t>II) Neoplasms</t>
         </is>
       </c>
     </row>
@@ -7304,79 +7019,79 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>Flatiron</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>II) Neoplasms</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>SLaM NHS</t>
+          <t>SAIL</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>V) Mental and behavioural disorders</t>
+          <t>IV) Endocrine, nutritional and metabolic diseases</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Flatiron</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>IX) Diseases of the circulatory system</t>
+          <t>II) Neoplasms</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>SLaM NHS</t>
+          <t>IQVIA</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>V) Mental and behavioural disorders</t>
+          <t>IV) Endocrine, nutritional and metabolic diseases</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>VUMC</t>
+          <t>Flatiron</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>IX) Diseases of the circulatory system</t>
+          <t>II) Neoplasms</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Flatiron</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>IV) Endocrine, nutritional and metabolic diseases</t>
+          <t>II) Neoplasms</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>VUMC</t>
+          <t>Flatiron</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -7388,72 +7103,67 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>VUMC</t>
+          <t>Flatiron</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>IX) Diseases of the circulatory system</t>
+          <t>II) Neoplasms</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>VUMC</t>
+          <t>SAIL</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>II) Neoplasms</t>
+          <t>IV) Endocrine, nutritional and metabolic diseases</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>IQVIA</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>IV) Endocrine, nutritional and metabolic diseases</t>
+          <t>other</t>
         </is>
       </c>
     </row>
     <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>Optum</t>
-        </is>
-      </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>V) Mental and behavioural disorders</t>
+          <t>other</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>IQVIA</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>II) Neoplasms</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Cerner</t>
+          <t>IBM</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>V) Mental and behavioural disorders</t>
         </is>
       </c>
     </row>
@@ -7465,14 +7175,14 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>IX) Diseases of the circulatory system</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>IBM</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -7484,456 +7194,386 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Flatiron</t>
+          <t>IBM</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>II) Neoplasms</t>
+          <t>other</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Flatiron</t>
+          <t>IBM</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>II) Neoplasms</t>
+          <t>V) Mental and behavioural disorders</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>IBM</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>X) Diseases of the respiratory system</t>
+          <t>other</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>IBM</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>V) Mental and behavioural disorders</t>
+          <t>I) Certain infectious and parasitic diseases</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Flatiron</t>
+          <t>IBM</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>II) Neoplasms</t>
+          <t>other</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>TriNetX</t>
+          <t>IBM</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>IV) Endocrine, nutritional and metabolic diseases</t>
+          <t>other</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Flatiron</t>
+          <t>IBM</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>II) Neoplasms</t>
+          <t>other</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>IBM</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>X) Diseases of the respiratory system</t>
+          <t>other</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Cerner</t>
+          <t>IBM</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>IV) Endocrine, nutritional and metabolic diseases</t>
+          <t>other</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>SLaM NHS</t>
+          <t>IBM</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>V) Mental and behavioural disorders</t>
+          <t>other</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>SAIL</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>IV) Endocrine, nutritional and metabolic diseases</t>
+          <t>V) Mental and behavioural disorders</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>VUMC</t>
+          <t>IBM</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>XIII) Diseases of the musculoskeletal system and connective tissue</t>
+          <t>other</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Cerner</t>
+          <t>IBM</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>IV) Endocrine, nutritional and metabolic diseases</t>
+          <t>V) Mental and behavioural disorders</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Flatiron</t>
+          <t>IBM</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>II) Neoplasms</t>
+          <t>IX) Diseases of the circulatory system</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>CPRD</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>V) Mental and behavioural disorders</t>
+          <t>I) Certain infectious and parasitic diseases</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>VUMC</t>
+          <t>CPRD</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>V) Mental and behavioural disorders</t>
+          <t>IV) Endocrine, nutritional and metabolic diseases</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Flatiron</t>
+          <t>IBM</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>II) Neoplasms</t>
+          <t>other</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>IBM</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>IV) Endocrine, nutritional and metabolic diseases</t>
+          <t>other</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Flatiron</t>
+          <t>IBM</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>II) Neoplasms</t>
+          <t>XXII) Codes for special purposes (COVID-19)</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>WADLS</t>
+          <t>SLaM NHS</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>V) Mental and behavioural disorders</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Flatiron</t>
+          <t>SLaM NHS</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>II) Neoplasms</t>
+          <t>V) Mental and behavioural disorders</t>
         </is>
       </c>
     </row>
     <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>VUMC</t>
-        </is>
-      </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>II) Neoplasms</t>
+          <t>IX) Diseases of the circulatory system</t>
         </is>
       </c>
     </row>
     <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>Flatiron</t>
-        </is>
-      </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>II) Neoplasms</t>
+          <t>IX) Diseases of the circulatory system</t>
         </is>
       </c>
     </row>
     <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>VUMC</t>
-        </is>
-      </c>
       <c r="B163" t="inlineStr">
         <is>
+          <t>V) Mental and behavioural disorders</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="B164" t="inlineStr">
+        <is>
           <t>IX) Diseases of the circulatory system</t>
         </is>
       </c>
     </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>Flatiron</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>II) Neoplasms</t>
-        </is>
-      </c>
-    </row>
     <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>WADLS</t>
-        </is>
-      </c>
       <c r="B165" t="inlineStr">
         <is>
+          <t>I) Certain infectious and parasitic diseases</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="B166" t="inlineStr">
+        <is>
           <t>IX) Diseases of the circulatory system</t>
         </is>
       </c>
     </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>Optum</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr">
+    <row r="167">
+      <c r="B167" t="inlineStr">
         <is>
           <t>XXII) Codes for special purposes (COVID-19)</t>
         </is>
       </c>
     </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>Flatiron</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>II) Neoplasms</t>
-        </is>
-      </c>
-    </row>
     <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>Cerner</t>
-        </is>
-      </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>X) Diseases of the respiratory system</t>
+          <t>V) Mental and behavioural disorders</t>
         </is>
       </c>
     </row>
     <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>SAIL</t>
-        </is>
-      </c>
       <c r="B169" t="inlineStr">
         <is>
+          <t>other</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>IX) Diseases of the circulatory system</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="B174" t="inlineStr">
+        <is>
           <t>I) Certain infectious and parasitic diseases</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>SAIL</t>
-        </is>
-      </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>XXII) Codes for special purposes (COVID-19)</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>Optum</t>
-        </is>
-      </c>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>I) Certain infectious and parasitic diseases</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>Flatiron</t>
-        </is>
-      </c>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>II) Neoplasms</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>VUMC</t>
-        </is>
-      </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>IX) Diseases of the circulatory system</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>Optum</t>
-        </is>
-      </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>II) Neoplasms</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>SAIL</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>IX) Diseases of the circulatory system</t>
+          <t>I) Certain infectious and parasitic diseases</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>SAIL</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>IX) Diseases of the circulatory system</t>
+          <t>XXII) Codes for special purposes (COVID-19)</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>NPS</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>IV) Endocrine, nutritional and metabolic diseases</t>
+          <t>V) Mental and behavioural disorders</t>
         </is>
       </c>
     </row>
@@ -7962,45 +7602,50 @@
       </c>
     </row>
     <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>SAIL</t>
+        </is>
+      </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>I) Certain infectious and parasitic diseases</t>
+          <t>other</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Flatiron</t>
+          <t>NPS</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>II) Neoplasms</t>
+          <t>other</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Flatiron</t>
+          <t>NPS</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>II) Neoplasms</t>
+          <t>other</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Flatiron</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>II) Neoplasms</t>
+          <t>IX) Diseases of the circulatory system</t>
         </is>
       </c>
     </row>
@@ -8012,19 +7657,19 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>IV) Endocrine, nutritional and metabolic diseases</t>
+          <t>II) Neoplasms</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Flatiron</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>II) Neoplasms</t>
+          <t>other</t>
         </is>
       </c>
     </row>
@@ -8036,19 +7681,19 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>X) Diseases of the respiratory system</t>
+          <t>XXII) Codes for special purposes (COVID-19)</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Flatiron</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>II) Neoplasms</t>
+          <t>other</t>
         </is>
       </c>
     </row>
@@ -8060,7 +7705,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>XXII) Codes for special purposes (COVID-19)</t>
         </is>
       </c>
     </row>
@@ -8072,43 +7717,43 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>IV) Endocrine, nutritional and metabolic diseases</t>
+          <t>XXII) Codes for special purposes (COVID-19)</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Flatiron</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>II) Neoplasms</t>
+          <t>other</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Flatiron</t>
+          <t>SAIL</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>II) Neoplasms</t>
+          <t>IV) Endocrine, nutritional and metabolic diseases</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>SAIL</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>XXII) Codes for special purposes (COVID-19)</t>
+          <t>other</t>
         </is>
       </c>
     </row>
@@ -8120,26 +7765,26 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>XIII) Diseases of the musculoskeletal system and connective tissue</t>
+          <t>XXII) Codes for special purposes (COVID-19)</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Flatiron</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>II) Neoplasms</t>
+          <t>other</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Cerner</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -8151,24 +7796,24 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Cerner</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>XIII) Diseases of the musculoskeletal system and connective tissue</t>
+          <t>other</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Flatiron</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>II) Neoplasms</t>
+          <t>V) Mental and behavioural disorders</t>
         </is>
       </c>
     </row>
@@ -8187,12 +7832,12 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>TriNetX</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>IX) Diseases of the circulatory system</t>
+          <t>other</t>
         </is>
       </c>
     </row>
@@ -8204,31 +7849,31 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>I) Certain infectious and parasitic diseases</t>
+          <t>other</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Flatiron</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>II) Neoplasms</t>
+          <t>V) Mental and behavioural disorders</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Flatiron</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>II) Neoplasms</t>
+          <t>other</t>
         </is>
       </c>
     </row>
@@ -8247,24 +7892,24 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Cerner</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>IX) Diseases of the circulatory system</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Flatiron</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>II) Neoplasms</t>
+          <t>XXII) Codes for special purposes (COVID-19)</t>
         </is>
       </c>
     </row>
@@ -8276,7 +7921,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>XXII) Codes for special purposes (COVID-19)</t>
+          <t>other</t>
         </is>
       </c>
     </row>
@@ -8300,19 +7945,19 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>IV) Endocrine, nutritional and metabolic diseases</t>
+          <t>other</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Cerner</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>XXII) Codes for special purposes (COVID-19)</t>
+          <t>other</t>
         </is>
       </c>
     </row>
@@ -8324,14 +7969,14 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>XXII) Codes for special purposes (COVID-19)</t>
+          <t>IX) Diseases of the circulatory system</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>SAIL</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -8343,36 +7988,36 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>SAIL</t>
+          <t>NPS</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>I) Certain infectious and parasitic diseases</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>SAIL</t>
+          <t>SLaM NHS</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>XXII) Codes for special purposes (COVID-19)</t>
+          <t>V) Mental and behavioural disorders</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Cerner</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>II) Neoplasms</t>
         </is>
       </c>
     </row>
@@ -8384,7 +8029,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>IX) Diseases of the circulatory system</t>
+          <t>IV) Endocrine, nutritional and metabolic diseases</t>
         </is>
       </c>
     </row>
@@ -8396,7 +8041,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>IX) Diseases of the circulatory system</t>
+          <t>IV) Endocrine, nutritional and metabolic diseases</t>
         </is>
       </c>
     </row>
@@ -8408,26 +8053,26 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>II) Neoplasms</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>VUMC</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>XIII) Diseases of the musculoskeletal system and connective tissue</t>
+          <t>IX) Diseases of the circulatory system</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Flatiron</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -8439,36 +8084,36 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>CPRD</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>IX) Diseases of the circulatory system</t>
+          <t>I) Certain infectious and parasitic diseases</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>SAIL</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>IX) Diseases of the circulatory system</t>
+          <t>XXII) Codes for special purposes (COVID-19)</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Flatiron</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>II) Neoplasms</t>
+          <t>IX) Diseases of the circulatory system</t>
         </is>
       </c>
     </row>
@@ -8480,7 +8125,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>V) Mental and behavioural disorders</t>
+          <t>IX) Diseases of the circulatory system</t>
         </is>
       </c>
     </row>
@@ -8492,19 +8137,19 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>XXII) Codes for special purposes (COVID-19)</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>SLaM NHS</t>
+          <t>InGef</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>V) Mental and behavioural disorders</t>
+          <t>other</t>
         </is>
       </c>
     </row>
@@ -8516,50 +8161,50 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>IX) Diseases of the circulatory system</t>
+          <t>other</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Flatiron</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>II) Neoplasms</t>
+          <t>IX) Diseases of the circulatory system</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Cerner</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>IX) Diseases of the circulatory system</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>CPRD</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>I) Certain infectious and parasitic diseases</t>
+          <t>IV) Endocrine, nutritional and metabolic diseases</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>VUMC</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -8571,47 +8216,57 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>SAIL</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>XXII) Codes for special purposes (COVID-19)</t>
+          <t>V) Mental and behavioural disorders</t>
         </is>
       </c>
     </row>
     <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>CPRD</t>
+        </is>
+      </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>IV) Endocrine, nutritional and metabolic diseases</t>
+          <t>V) Mental and behavioural disorders</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>SLaM NHS</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>V) Mental and behavioural disorders</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>SAIL</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>XXII) Codes for special purposes (COVID-19)</t>
+          <t>IX) Diseases of the circulatory system</t>
         </is>
       </c>
     </row>
     <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>SAIL</t>
+        </is>
+      </c>
       <c r="B235" t="inlineStr">
         <is>
           <t>other</t>
@@ -8619,9 +8274,14 @@
       </c>
     </row>
     <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>CPRD</t>
+        </is>
+      </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>VI) Diseases of the nervous system</t>
+          <t>other</t>
         </is>
       </c>
     </row>
@@ -8633,26 +8293,26 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>V) Mental and behavioural disorders</t>
+          <t>other</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>SLaM NHS</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>V) Mental and behavioural disorders</t>
+          <t>other</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>SAIL</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -8664,7 +8324,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>SAIL</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -8676,43 +8336,43 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>CPRD</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>XIII) Diseases of the musculoskeletal system and connective tissue</t>
+          <t>V) Mental and behavioural disorders</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>CPRD</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>XIII) Diseases of the musculoskeletal system and connective tissue</t>
+          <t>other</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>VUMC</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>IV) Endocrine, nutritional and metabolic diseases</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>Cerner</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -8724,60 +8384,60 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>Flatiron</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>II) Neoplasms</t>
+          <t>IV) Endocrine, nutritional and metabolic diseases</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>Flatiron</t>
+          <t>SLaM NHS</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>II) Neoplasms</t>
+          <t>V) Mental and behavioural disorders</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>TriNetX</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>IX) Diseases of the circulatory system</t>
+          <t>XXII) Codes for special purposes (COVID-19)</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>CPRD</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>XIII) Diseases of the musculoskeletal system and connective tissue</t>
+          <t>I) Certain infectious and parasitic diseases</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>Flatiron</t>
+          <t>CPRD</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>II) Neoplasms</t>
+          <t>other</t>
         </is>
       </c>
     </row>
@@ -8801,98 +8461,103 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>V) Mental and behavioural disorders</t>
+          <t>I) Certain infectious and parasitic diseases</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>SAIL</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>V) Mental and behavioural disorders</t>
+          <t>II) Neoplasms</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>CPRD</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>X) Diseases of the respiratory system</t>
+          <t>IX) Diseases of the circulatory system</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>CPRD</t>
+          <t>SLaM NHS</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>X) Diseases of the respiratory system</t>
+          <t>V) Mental and behavioural disorders</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>CPRD</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>I) Certain infectious and parasitic diseases</t>
+          <t>IX) Diseases of the circulatory system</t>
         </is>
       </c>
     </row>
     <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>IV) Endocrine, nutritional and metabolic diseases</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>SLaM NHS</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>V) Mental and behavioural disorders</t>
+          <t>IV) Endocrine, nutritional and metabolic diseases</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>VUMC</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>IX) Diseases of the circulatory system</t>
+          <t>other</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>TriNetX</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>XXII) Codes for special purposes (COVID-19)</t>
+          <t>other</t>
         </is>
       </c>
     </row>
@@ -8904,7 +8569,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>XXII) Codes for special purposes (COVID-19)</t>
+          <t>IV) Endocrine, nutritional and metabolic diseases</t>
         </is>
       </c>
     </row>
@@ -8916,7 +8581,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>X) Diseases of the respiratory system</t>
+          <t>other</t>
         </is>
       </c>
     </row>
@@ -8928,43 +8593,43 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>X) Diseases of the respiratory system</t>
+          <t>other</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>CPRD</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>I) Certain infectious and parasitic diseases</t>
+          <t>XXII) Codes for special purposes (COVID-19)</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>SLaM NHS</t>
+          <t>CPRD</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>V) Mental and behavioural disorders</t>
+          <t>I) Certain infectious and parasitic diseases</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>CPRD</t>
+          <t>SLaM NHS</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>X) Diseases of the respiratory system</t>
+          <t>V) Mental and behavioural disorders</t>
         </is>
       </c>
     </row>
@@ -8993,21 +8658,26 @@
       </c>
     </row>
     <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>I) Certain infectious and parasitic diseases</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>Flatiron</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>II) Neoplasms</t>
+          <t>I) Certain infectious and parasitic diseases</t>
         </is>
       </c>
     </row>
@@ -9019,7 +8689,7 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>IX) Diseases of the circulatory system</t>
         </is>
       </c>
     </row>
@@ -9038,339 +8708,369 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>Flatiron</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>II) Neoplasms</t>
+          <t>IX) Diseases of the circulatory system</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>SLaM NHS</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>V) Mental and behavioural disorders</t>
+          <t>IV) Endocrine, nutritional and metabolic diseases</t>
         </is>
       </c>
     </row>
     <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>II) Neoplasms</t>
+          <t>IX) Diseases of the circulatory system</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>CPRD</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>VI) Diseases of the nervous system</t>
+          <t>IX) Diseases of the circulatory system</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>SAIL</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>VI) Diseases of the nervous system</t>
+          <t>other</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>SLaM NHS</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>V) Mental and behavioural disorders</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>SLaM NHS</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>V) Mental and behavioural disorders</t>
+          <t>IX) Diseases of the circulatory system</t>
         </is>
       </c>
     </row>
     <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>InGef</t>
+        </is>
+      </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>V) Mental and behavioural disorders</t>
+          <t>II) Neoplasms</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>CPRD</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>IX) Diseases of the circulatory system</t>
+          <t>other</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>CPRD</t>
+          <t>SAIL</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>XXII) Codes for special purposes (COVID-19)</t>
+          <t>other</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>CPRD</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>I) Certain infectious and parasitic diseases</t>
+          <t>IX) Diseases of the circulatory system</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>SAIL</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>XIII) Diseases of the musculoskeletal system and connective tissue</t>
+          <t>V) Mental and behavioural disorders</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>Flatiron</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>II) Neoplasms</t>
+          <t>other</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>Flatiron</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>II) Neoplasms</t>
+          <t>IX) Diseases of the circulatory system</t>
         </is>
       </c>
     </row>
     <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>XXII) Codes for special purposes (COVID-19)</t>
+          <t>other</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>Flatiron</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>II) Neoplasms</t>
+          <t>XXII) Codes for special purposes (COVID-19)</t>
         </is>
       </c>
     </row>
     <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>SLaM NHS</t>
+        </is>
+      </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>II) Neoplasms</t>
+          <t>V) Mental and behavioural disorders</t>
         </is>
       </c>
     </row>
     <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>InGef</t>
+        </is>
+      </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>V) Mental and behavioural disorders</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>SLaM NHS</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>V) Mental and behavioural disorders</t>
+          <t>XXII) Codes for special purposes (COVID-19)</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>SLaM NHS</t>
+          <t>CPRD</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>V) Mental and behavioural disorders</t>
+          <t>XXII) Codes for special purposes (COVID-19)</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>SAIL</t>
+          <t>CPRD</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>IX) Diseases of the circulatory system</t>
+          <t>I) Certain infectious and parasitic diseases</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>SLaM NHS</t>
+          <t>SAIL</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>V) Mental and behavioural disorders</t>
+          <t>other</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>SLaM NHS</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>V) Mental and behavioural disorders</t>
+          <t>other</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>SAIL</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>XIII) Diseases of the musculoskeletal system and connective tissue</t>
+          <t>XXII) Codes for special purposes (COVID-19)</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>SAIL</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>II) Neoplasms</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>TriNetX</t>
+          <t>InGef</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>II) Neoplasms</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>CPRD</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>IV) Endocrine, nutritional and metabolic diseases</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>SAIL</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>IV) Endocrine, nutritional and metabolic diseases</t>
+          <t>I) Certain infectious and parasitic diseases</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>VUMC</t>
+          <t>InGef</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>II) Neoplasms</t>
+          <t>other</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>CPRD</t>
+          <t>SLaM NHS</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>IX) Diseases of the circulatory system</t>
+          <t>V) Mental and behavioural disorders</t>
         </is>
       </c>
     </row>
     <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
       <c r="B302" t="inlineStr">
         <is>
           <t>other</t>
@@ -9380,19 +9080,24 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
+          <t>SLaM NHS</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>V) Mental and behavioural disorders</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
           <t>SAIL</t>
         </is>
       </c>
-      <c r="B303" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-    </row>
-    <row r="304">
       <c r="B304" t="inlineStr">
         <is>
-          <t>II) Neoplasms</t>
+          <t>IX) Diseases of the circulatory system</t>
         </is>
       </c>
     </row>
@@ -9411,60 +9116,60 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>VUMC</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>IX) Diseases of the circulatory system</t>
+          <t>II) Neoplasms</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>CPRD</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>I) Certain infectious and parasitic diseases</t>
+          <t>IX) Diseases of the circulatory system</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>SLaM NHS</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>V) Mental and behavioural disorders</t>
+          <t>IX) Diseases of the circulatory system</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>CPRD</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>XIII) Diseases of the musculoskeletal system and connective tissue</t>
+          <t>other</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>SLaM NHS</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>V) Mental and behavioural disorders</t>
+          <t>other</t>
         </is>
       </c>
     </row>
@@ -9483,12 +9188,12 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>CPRD</t>
+          <t>SAIL</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>V) Mental and behavioural disorders</t>
+          <t>other</t>
         </is>
       </c>
     </row>
@@ -9500,43 +9205,43 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>VI) Diseases of the nervous system</t>
+          <t>other</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>SAIL</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>V) Mental and behavioural disorders</t>
+          <t>XXII) Codes for special purposes (COVID-19)</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>SAIL</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>IX) Diseases of the circulatory system</t>
+          <t>other</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>SAIL</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>XXII) Codes for special purposes (COVID-19)</t>
+          <t>IV) Endocrine, nutritional and metabolic diseases</t>
         </is>
       </c>
     </row>
@@ -9548,71 +9253,76 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>I) Certain infectious and parasitic diseases</t>
+          <t>other</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>Flatiron</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>II) Neoplasms</t>
+          <t>IV) Endocrine, nutritional and metabolic diseases</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>VUMC</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>VI) Diseases of the nervous system</t>
+          <t>IX) Diseases of the circulatory system</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>Flatiron</t>
+          <t>SAIL</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>II) Neoplasms</t>
+          <t>IV) Endocrine, nutritional and metabolic diseases</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>SAIL</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>II) Neoplasms</t>
+          <t>XXII) Codes for special purposes (COVID-19)</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>SAIL</t>
+          <t>CPRD</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>IX) Diseases of the circulatory system</t>
+          <t>other</t>
         </is>
       </c>
     </row>
     <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
       <c r="B323" t="inlineStr">
         <is>
           <t>II) Neoplasms</t>
@@ -9622,36 +9332,36 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>CPRD</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>V) Mental and behavioural disorders</t>
+          <t>XXII) Codes for special purposes (COVID-19)</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>CPRD</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>IV) Endocrine, nutritional and metabolic diseases</t>
+          <t>IX) Diseases of the circulatory system</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>Flatiron</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>II) Neoplasms</t>
+          <t>IX) Diseases of the circulatory system</t>
         </is>
       </c>
     </row>
@@ -9670,86 +9380,91 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>Flatiron</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>II) Neoplasms</t>
+          <t>V) Mental and behavioural disorders</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>SLaM NHS</t>
+          <t>SAIL</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>V) Mental and behavioural disorders</t>
+          <t>other</t>
         </is>
       </c>
     </row>
     <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>CPRD</t>
+        </is>
+      </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>VI) Diseases of the nervous system</t>
+          <t>other</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>CPRD</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>VI) Diseases of the nervous system</t>
+          <t>other</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>SAIL</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>VI) Diseases of the nervous system</t>
+          <t>I) Certain infectious and parasitic diseases</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>CPRD</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>XXII) Codes for special purposes (COVID-19)</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>CPRD</t>
+          <t>InGef</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>I) Certain infectious and parasitic diseases</t>
+          <t>II) Neoplasms</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>CPRD</t>
+          <t>SLaM NHS</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
@@ -9761,7 +9476,7 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>SAIL</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
@@ -9773,48 +9488,48 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>CPRD</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>IV) Endocrine, nutritional and metabolic diseases</t>
+          <t>II) Neoplasms</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>SAIL</t>
+          <t>Flatiron</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>IV) Endocrine, nutritional and metabolic diseases</t>
+          <t>II) Neoplasms</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>SAIL</t>
+          <t>CPRD</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>V) Mental and behavioural disorders</t>
+          <t>I) Certain infectious and parasitic diseases</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>SAIL</t>
+          <t>SLaM NHS</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>X) Diseases of the respiratory system</t>
+          <t>V) Mental and behavioural disorders</t>
         </is>
       </c>
     </row>
@@ -9826,316 +9541,331 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>IX) Diseases of the circulatory system</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>SLaM NHS</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>II) Neoplasms</t>
+          <t>V) Mental and behavioural disorders</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>Flatiron</t>
+          <t>SLaM NHS</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>II) Neoplasms</t>
+          <t>V) Mental and behavioural disorders</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>CPRD</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>IX) Diseases of the circulatory system</t>
+          <t>other</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>TriNetX</t>
+          <t>CPRD</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>IV) Endocrine, nutritional and metabolic diseases</t>
+          <t>V) Mental and behavioural disorders</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>VUMC</t>
+          <t>SAIL</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>IX) Diseases of the circulatory system</t>
+          <t>other</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>Flatiron</t>
+          <t>CPRD</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>II) Neoplasms</t>
+          <t>V) Mental and behavioural disorders</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>VUMC</t>
+          <t>SAIL</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>V) Mental and behavioural disorders</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>VUMC</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>IV) Endocrine, nutritional and metabolic diseases</t>
+          <t>I) Certain infectious and parasitic diseases</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>Flatiron</t>
+          <t>IBM</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>II) Neoplasms</t>
+          <t>I) Certain infectious and parasitic diseases</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>VUMC</t>
+          <t>CPRD</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>V) Mental and behavioural disorders</t>
+          <t>other</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>SAIL</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>IX) Diseases of the circulatory system</t>
+          <t>V) Mental and behavioural disorders</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>NPS</t>
+          <t>SAIL</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>IX) Diseases of the circulatory system</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>VUMC</t>
+          <t>SAIL</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>X) Diseases of the respiratory system</t>
+          <t>XXII) Codes for special purposes (COVID-19)</t>
         </is>
       </c>
     </row>
     <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>CPRD</t>
+        </is>
+      </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>IV) Endocrine, nutritional and metabolic diseases</t>
+          <t>I) Certain infectious and parasitic diseases</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>NPS</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>I) Certain infectious and parasitic diseases</t>
+          <t>IX) Diseases of the circulatory system</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>NPS</t>
+          <t>IBM</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>X) Diseases of the respiratory system</t>
+          <t>IX) Diseases of the circulatory system</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>Flatiron</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>II) Neoplasms</t>
+          <t>other</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>Flatiron</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>II) Neoplasms</t>
+          <t>other</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>SLaM NHS</t>
+          <t>SAIL</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>V) Mental and behavioural disorders</t>
+          <t>IX) Diseases of the circulatory system</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>InGef</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>II) Neoplasms</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>Flatiron</t>
+          <t>CPRD</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>II) Neoplasms</t>
+          <t>V) Mental and behavioural disorders</t>
         </is>
       </c>
     </row>
     <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>SLaM NHS</t>
+        </is>
+      </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>V) Mental and behavioural disorders</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>CPRD</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>II) Neoplasms</t>
+          <t>other</t>
         </is>
       </c>
     </row>
     <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>InGef</t>
+        </is>
+      </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>IX) Diseases of the circulatory system</t>
+          <t>other</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>TriNetX</t>
+          <t>SAIL</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>IX) Diseases of the circulatory system</t>
+          <t>other</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>SLaM NHS</t>
+          <t>CPRD</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>V) Mental and behavioural disorders</t>
+          <t>other</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>TriNetX</t>
+          <t>CPRD</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>XXII) Codes for special purposes (COVID-19)</t>
+          <t>I) Certain infectious and parasitic diseases</t>
         </is>
       </c>
     </row>
@@ -10147,21 +9877,26 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>V) Mental and behavioural disorders</t>
         </is>
       </c>
     </row>
     <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>CPRD</t>
+        </is>
+      </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>IX) Diseases of the circulatory system</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>SAIL</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
@@ -10173,134 +9908,139 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>Flatiron</t>
+          <t>SAIL</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>II) Neoplasms</t>
+          <t>IV) Endocrine, nutritional and metabolic diseases</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>CPRD</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>XXII) Codes for special purposes (COVID-19)</t>
+          <t>IV) Endocrine, nutritional and metabolic diseases</t>
         </is>
       </c>
     </row>
     <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>CPRD</t>
+        </is>
+      </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>XXII) Codes for special purposes (COVID-19)</t>
+          <t>other</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>Flatiron</t>
+          <t>SAIL</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>II) Neoplasms</t>
+          <t>V) Mental and behavioural disorders</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>SAIL</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>XIII) Diseases of the musculoskeletal system and connective tissue</t>
+          <t>other</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>VUMC</t>
+          <t>CPRD</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>II) Neoplasms</t>
+          <t>other</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>SAIL</t>
+          <t>TriNetX</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>V) Mental and behavioural disorders</t>
+          <t>other</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>Flatiron</t>
+          <t>TriNetX</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>II) Neoplasms</t>
+          <t>XXII) Codes for special purposes (COVID-19)</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>TriNetX</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>IV) Endocrine, nutritional and metabolic diseases</t>
+          <t>II) Neoplasms</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>Flatiron</t>
+          <t>TriNetX</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>II) Neoplasms</t>
+          <t>IV) Endocrine, nutritional and metabolic diseases</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>Flatiron</t>
+          <t>TriNetX</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>II) Neoplasms</t>
+          <t>IX) Diseases of the circulatory system</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>VUMC</t>
+          <t>TriNetX</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
@@ -10310,35 +10050,45 @@
       </c>
     </row>
     <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>TriNetX</t>
+        </is>
+      </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>V) Mental and behavioural disorders</t>
+          <t>XXII) Codes for special purposes (COVID-19)</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>Flatiron</t>
+          <t>TriNetX</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>II) Neoplasms</t>
+          <t>other</t>
         </is>
       </c>
     </row>
     <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>TriNetX</t>
+        </is>
+      </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>XXII) Codes for special purposes (COVID-19)</t>
+          <t>IV) Endocrine, nutritional and metabolic diseases</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>Cerner</t>
+          <t>TriNetX</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
@@ -10350,151 +10100,151 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>TriNetX</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>IV) Endocrine, nutritional and metabolic diseases</t>
+          <t>XXII) Codes for special purposes (COVID-19)</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>SLaM NHS</t>
+          <t>TriNetX</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>V) Mental and behavioural disorders</t>
+          <t>II) Neoplasms</t>
         </is>
       </c>
     </row>
     <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>TriNetX</t>
+        </is>
+      </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>IV) Endocrine, nutritional and metabolic diseases</t>
+          <t>XXII) Codes for special purposes (COVID-19)</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>Flatiron</t>
+          <t>TriNetX</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>II) Neoplasms</t>
+          <t>V) Mental and behavioural disorders</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>Flatiron</t>
+          <t>TriNetX</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>II) Neoplasms</t>
+          <t>IX) Diseases of the circulatory system</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>CPRD</t>
+          <t>NPS</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>X) Diseases of the respiratory system</t>
+          <t>other</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>NPS</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>IX) Diseases of the circulatory system</t>
+          <t>I) Certain infectious and parasitic diseases</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>VUMC</t>
+          <t>NPS</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>IX) Diseases of the circulatory system</t>
+          <t>other</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>Flatiron</t>
+          <t>SLaM NHS</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>II) Neoplasms</t>
+          <t>V) Mental and behavioural disorders</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>Flatiron</t>
+          <t>InGef</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>II) Neoplasms</t>
+          <t>other</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>InGef</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>II) Neoplasms</t>
+          <t>IX) Diseases of the circulatory system</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>Flatiron</t>
+          <t>SLaM NHS</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>II) Neoplasms</t>
+          <t>V) Mental and behavioural disorders</t>
         </is>
       </c>
     </row>
     <row r="400">
-      <c r="A400" t="inlineStr">
-        <is>
-          <t>SAIL</t>
-        </is>
-      </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>IX) Diseases of the circulatory system</t>
+          <t>other</t>
         </is>
       </c>
     </row>
@@ -10506,26 +10256,31 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>XXII) Codes for special purposes (COVID-19)</t>
+          <t>V) Mental and behavioural disorders</t>
         </is>
       </c>
     </row>
     <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>VUMC</t>
+        </is>
+      </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>VI) Diseases of the nervous system</t>
+          <t>V) Mental and behavioural disorders</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>TriNetX</t>
+          <t>VUMC</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>II) Neoplasms</t>
+          <t>other</t>
         </is>
       </c>
     </row>
@@ -10537,129 +10292,134 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>IX) Diseases of the circulatory system</t>
+          <t>other</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>TriNetX</t>
+          <t>VUMC</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>XXII) Codes for special purposes (COVID-19)</t>
+          <t>other</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>Flatiron</t>
+          <t>VUMC</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>II) Neoplasms</t>
+          <t>other</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>Flatiron</t>
+          <t>VUMC</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>II) Neoplasms</t>
+          <t>other</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>VUMC</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>XXII) Codes for special purposes (COVID-19)</t>
+          <t>II) Neoplasms</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>SLaM NHS</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>IX) Diseases of the circulatory system</t>
+          <t>V) Mental and behavioural disorders</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>SAIL</t>
+          <t>VUMC</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>VI) Diseases of the nervous system</t>
+          <t>V) Mental and behavioural disorders</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>CPRD</t>
+          <t>VUMC</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>VI) Diseases of the nervous system</t>
+          <t>V) Mental and behavioural disorders</t>
         </is>
       </c>
     </row>
     <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>InGef</t>
+        </is>
+      </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>II) Neoplasms</t>
+          <t>IV) Endocrine, nutritional and metabolic diseases</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>VUMC</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>I) Certain infectious and parasitic diseases</t>
+          <t>IX) Diseases of the circulatory system</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>VUMC</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>V) Mental and behavioural disorders</t>
+          <t>IV) Endocrine, nutritional and metabolic diseases</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>VUMC</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
@@ -10671,12 +10431,12 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>VUMC</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>I) Certain infectious and parasitic diseases</t>
+          <t>other</t>
         </is>
       </c>
     </row>
@@ -10695,19 +10455,19 @@
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>TriNetX</t>
+          <t>VUMC</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>V) Mental and behavioural disorders</t>
+          <t>IX) Diseases of the circulatory system</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>TriNetX</t>
+          <t>VUMC</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
@@ -10719,7 +10479,7 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>Flatiron</t>
+          <t>VUMC</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
@@ -10736,7 +10496,7 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>I) Certain infectious and parasitic diseases</t>
+          <t>IX) Diseases of the circulatory system</t>
         </is>
       </c>
     </row>
@@ -10748,31 +10508,355 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>I) Certain infectious and parasitic diseases</t>
+          <t>II) Neoplasms</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>Flatiron</t>
+          <t>VUMC</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>II) Neoplasms</t>
+          <t>other</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>CPRD</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
         <is>
           <t>other</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>SAIL</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>IX) Diseases of the circulatory system</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>VUMC</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>V) Mental and behavioural disorders</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>VUMC</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>II) Neoplasms</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>VUMC</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>IX) Diseases of the circulatory system</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>VUMC</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>IX) Diseases of the circulatory system</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>VUMC</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>IX) Diseases of the circulatory system</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>VUMC</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>VUMC</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>IV) Endocrine, nutritional and metabolic diseases</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>VUMC</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>VUMC</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>IX) Diseases of the circulatory system</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>VUMC</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>II) Neoplasms</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>SAIL</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>CPRD</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>VUMC</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>VUMC</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>VUMC</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>IX) Diseases of the circulatory system</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>VUMC</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>VUMC</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>IV) Endocrine, nutritional and metabolic diseases</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>VUMC</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>V) Mental and behavioural disorders</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>VUMC</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>VUMC</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>II) Neoplasms</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>VUMC</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>IX) Diseases of the circulatory system</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>VUMC</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>IX) Diseases of the circulatory system</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>VUMC</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>IX) Diseases of the circulatory system</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>VUMC</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>VUMC</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>I) Certain infectious and parasitic diseases</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>VUMC</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>I) Certain infectious and parasitic diseases</t>
         </is>
       </c>
     </row>
@@ -10819,7 +10903,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -10827,7 +10911,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.16239316239316</v>
+        <v>18.25902335456476</v>
       </c>
     </row>
     <row r="3">
@@ -10837,7 +10921,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -10845,7 +10929,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>13.67521367521367</v>
+        <v>13.69426751592357</v>
       </c>
     </row>
     <row r="4">
@@ -10855,7 +10939,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -10863,7 +10947,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>12.39316239316239</v>
+        <v>12.4203821656051</v>
       </c>
     </row>
     <row r="5">
@@ -10873,7 +10957,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -10881,7 +10965,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>9.081196581196581</v>
+        <v>9.235668789808917</v>
       </c>
     </row>
     <row r="6">
@@ -10899,7 +10983,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>8.44017094017094</v>
+        <v>8.386411889596603</v>
       </c>
     </row>
     <row r="7">
@@ -10909,7 +10993,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -10917,7 +11001,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>6.730769230769231</v>
+        <v>6.475583864118896</v>
       </c>
     </row>
     <row r="8">
@@ -10927,7 +11011,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -10935,7 +11019,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>31.51709401709402</v>
+        <v>31.52866242038217</v>
       </c>
     </row>
   </sheetData>
